--- a/신분당-성남시-보고서.xlsx
+++ b/신분당-성남시-보고서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 내 문서 모음\01. 업무관련 문서양식\017 지하안전점검(지하안전법) 관련\■ 연도별 지하안전점검(육안점검) 결과보고서\2026년 지하안전점검 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DBF222-26B7-40E8-A614-48E7B0262FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794FA71A-814B-4218-96D7-73EF5C6A6307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1012,16 +1012,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6090,66 +6090,66 @@
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="13"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14" t="str">
+      <c r="B5" s="11"/>
+      <c r="C5" s="9" t="str">
         <f>RawData!C2</f>
         <v>성남시</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14" t="s">
+      <c r="F5" s="11"/>
+      <c r="G5" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="14" t="str">
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="9" t="str">
         <f>RawData!B2</f>
         <v>신분당선㈜</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="14" t="s">
+      <c r="K5" s="10"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="13"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
@@ -6170,43 +6170,43 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="11" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="9" t="s">
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" s="12" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
@@ -6237,9 +6237,9 @@
       <c r="M8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -8226,6 +8226,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="N7:N8"/>
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
@@ -8238,14 +8246,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="N7:N8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
